--- a/data/50001588 - ZITRON PERU HUARON.xlsx
+++ b/data/50001588 - ZITRON PERU HUARON.xlsx
@@ -2333,7 +2333,7 @@
         <v>46252.5539821875</v>
       </c>
       <c r="D11" s="9">
-        <v>46252.5539969213</v>
+        <v>46278.82959365741</v>
       </c>
       <c r="E11" s="10" t="s">
         <v>41</v>
